--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-11-2025.xlsx
@@ -589,26 +589,26 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff69769a235
+	0x7ff6973f2630
+	0x7ff6971816dd
+	0x7ff6971da27e
+	0x7ff6971da58c
+	0x7ff69722ed77
+	0x7ff69722baba
+	0x7ff6971cb0ed
+	0x7ff6971cbf63
+	0x7ff6976c5d60
+	0x7ff6976bfe8a
+	0x7ff6976e1005
+	0x7ff69740d71e
+	0x7ff697414e1f
+	0x7ff6973fb7c4
+	0x7ff6973fb97f
+	0x7ff6973e18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -616,7 +616,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>£9.77</t>
+          <t>Error: 502 Server Error: Bad Gateway for url: https://www.insulation-online.com/product/celotex-tb4025-25mm/</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -709,26 +709,26 @@
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -829,26 +829,26 @@
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -949,26 +949,26 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1069,26 +1069,26 @@
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1189,26 +1189,26 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1309,26 +1309,26 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1429,26 +1429,26 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1549,26 +1549,26 @@
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1669,26 +1669,26 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1789,26 +1789,26 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>£50.96</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1909,26 +1909,26 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2029,26 +2029,26 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2149,26 +2149,26 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2269,26 +2269,26 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2486,26 +2486,26 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2606,26 +2606,26 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2726,26 +2726,26 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2846,26 +2846,26 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2966,26 +2966,26 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3086,26 +3086,26 @@
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3206,26 +3206,26 @@
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3326,26 +3326,26 @@
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3446,26 +3446,26 @@
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff76e4aa235
-	0x7ff76e202630
-	0x7ff76df916dd
-	0x7ff76dfea27e
-	0x7ff76dfea58c
-	0x7ff76e03ed77
-	0x7ff76e03baba
-	0x7ff76dfdb0ed
-	0x7ff76dfdbf63
-	0x7ff76e4d5d60
-	0x7ff76e4cfe8a
-	0x7ff76e4f1005
-	0x7ff76e21d71e
-	0x7ff76e224e1f
-	0x7ff76e20b7c4
-	0x7ff76e20b97f
-	0x7ff76e1f18e8
+	0x7ff60a0ea235
+	0x7ff609e42630
+	0x7ff609bd16dd
+	0x7ff609c2a27e
+	0x7ff609c2a58c
+	0x7ff609c7ed77
+	0x7ff609c7baba
+	0x7ff609c1b0ed
+	0x7ff609c1bf63
+	0x7ff60a115d60
+	0x7ff60a10fe8a
+	0x7ff60a131005
+	0x7ff609e5d71e
+	0x7ff609e64e1f
+	0x7ff609e4b7c4
+	0x7ff609e4b97f
+	0x7ff609e318e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-11-2025.xlsx
@@ -588,35 +588,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff69769a235
-	0x7ff6973f2630
-	0x7ff6971816dd
-	0x7ff6971da27e
-	0x7ff6971da58c
-	0x7ff69722ed77
-	0x7ff69722baba
-	0x7ff6971cb0ed
-	0x7ff6971cbf63
-	0x7ff6976c5d60
-	0x7ff6976bfe8a
-	0x7ff6976e1005
-	0x7ff69740d71e
-	0x7ff697414e1f
-	0x7ff6973fb7c4
-	0x7ff6973fb97f
-	0x7ff6973e18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£12.08</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://www.insulation-online.com/product/celotex-tb4025-25mm/</t>
+          <t>£9.77</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -708,30 +685,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£14.53</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -828,30 +782,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£18.03</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -948,30 +879,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£19.41</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1068,30 +976,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£22.98</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1188,30 +1073,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£26.29</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1308,30 +1170,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£25.33</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1428,30 +1267,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£28.46</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1548,30 +1364,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£32.53</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1668,30 +1461,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£31.71</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1788,30 +1558,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£39.35</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1826,7 +1573,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£50.96</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1908,30 +1655,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£39.03</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2028,30 +1752,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£46.53</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2148,30 +1849,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£49.78</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2268,30 +1946,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£46.97</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2485,30 +2140,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£1,022.90</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2605,30 +2237,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£34.56</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2725,30 +2334,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£41.09</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2845,30 +2431,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£48.75</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2965,30 +2528,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£53.63</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3085,30 +2625,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£58.14</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3205,30 +2722,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£57.29</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3325,30 +2819,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£938.88</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3445,30 +2916,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.164); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a0ea235
-	0x7ff609e42630
-	0x7ff609bd16dd
-	0x7ff609c2a27e
-	0x7ff609c2a58c
-	0x7ff609c7ed77
-	0x7ff609c7baba
-	0x7ff609c1b0ed
-	0x7ff609c1bf63
-	0x7ff60a115d60
-	0x7ff60a10fe8a
-	0x7ff60a131005
-	0x7ff609e5d71e
-	0x7ff609e64e1f
-	0x7ff609e4b7c4
-	0x7ff609e4b97f
-	0x7ff609e318e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£55.22</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
